--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05 12:08:34</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CAe62bbd8b43019b0f030c2e817fa839a0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>basic course information</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
